--- a/results/Int All Data -0.8/Rando_9_permute.xlsx
+++ b/results/Int All Data -0.8/Rando_9_permute.xlsx
@@ -440,1487 +440,1487 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.908467533513684</v>
+        <v>0.9095813558525598</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9087704488853385</v>
+        <v>0.9086167256274795</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9100752505554848</v>
+        <v>0.90771267847673</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9059790963220535</v>
+        <v>0.9048654418033282</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9048886009840974</v>
+        <v>0.902577381871396</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9082391302888519</v>
+        <v>0.9021579993152937</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9082391302888519</v>
+        <v>0.9012678812370359</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9132440306372467</v>
+        <v>0.8982900804865441</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9160540112372373</v>
+        <v>0.8971856560760963</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9109373426686089</v>
+        <v>0.8981689143378824</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9109373426686089</v>
+        <v>0.8971856560760963</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9109373426686089</v>
+        <v>0.8970831179641402</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.917452120911062</v>
+        <v>0.8988912122656392</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9150242667937625</v>
+        <v>0.9010208499754983</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8946368036302854</v>
+        <v>0.8986722069692352</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8946368036302854</v>
+        <v>0.8997393753062718</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8943758432962563</v>
+        <v>0.9011839711617853</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8890354704670099</v>
+        <v>0.9011653431250797</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8907410266565527</v>
+        <v>0.9026985480200578</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8902191059884943</v>
+        <v>0.8948975961441643</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8790025105894514</v>
+        <v>0.891146312320013</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8751253616524244</v>
+        <v>0.8885553370164263</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.881644671038941</v>
+        <v>0.8910671012089764</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8793985661446342</v>
+        <v>0.8910671012089764</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8824881351153595</v>
+        <v>0.8957457591847968</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8828096785237197</v>
+        <v>0.8928891245829669</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8886625740925964</v>
+        <v>0.8888721814605723</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8868964348287227</v>
+        <v>0.8888721814605723</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8867333136424357</v>
+        <v>0.8872877914196914</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8866727305681048</v>
+        <v>0.8897762286113218</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8849624754143479</v>
+        <v>0.8883875168659251</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.881127281514946</v>
+        <v>0.8874834697151757</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8798644348824252</v>
+        <v>0.887846968161161</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8827955816310776</v>
+        <v>0.8875860078271318</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8835784626331653</v>
+        <v>0.884892494411589</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8734243366069451</v>
+        <v>0.8838672811121777</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8699898972269398</v>
+        <v>0.8937184917667433</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8699898972269398</v>
+        <v>0.8940400351751036</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8740813524961569</v>
+        <v>0.8853769911860857</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8756284864636267</v>
+        <v>0.8841094455893508</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8700410823728426</v>
+        <v>0.8853350361484604</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.871606844377018</v>
+        <v>0.8869613812269668</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8669840705113144</v>
+        <v>0.8781632420167954</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8616623257187737</v>
+        <v>0.877641321348737</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8629298713155086</v>
+        <v>0.8775807382744061</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8598403023447831</v>
+        <v>0.8866539347112486</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8639225275057226</v>
+        <v>0.8893613771992831</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8634798179487007</v>
+        <v>0.8906895058703489</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8621750162785546</v>
+        <v>0.8891423719028791</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.862757520020944</v>
+        <v>0.8870127341930201</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8631582745403406</v>
+        <v>0.8850834737428592</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8671565896260296</v>
+        <v>0.8833034054064939</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8674781330343897</v>
+        <v>0.8816770603279878</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8479851512730836</v>
+        <v>0.8816770603279878</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8247548147601178</v>
+        <v>0.8850275896327424</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8240138887956554</v>
+        <v>0.8784382992434667</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8224061717538549</v>
+        <v>0.8758239969389605</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.813295719243601</v>
+        <v>0.8848085843363385</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8075451939665299</v>
+        <v>0.8814300290664501</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8046652323637804</v>
+        <v>0.8795937409796668</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8046652323637804</v>
+        <v>0.8804977881304163</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8044042720297512</v>
+        <v>0.8728693553692379</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8077502701904423</v>
+        <v>0.8735124421859581</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8062031362229726</v>
+        <v>0.8700360477683275</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8042505487718921</v>
+        <v>0.8676315206519478</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8023165893575174</v>
+        <v>0.88065637817264</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7631394786834844</v>
+        <v>0.8807169612469709</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7547140680275761</v>
+        <v>0.8803954178386106</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7564196242171191</v>
+        <v>0.8798129140962214</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7496672126415563</v>
+        <v>0.874919949788211</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7360131973766354</v>
+        <v>0.879463512542878</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7355518597829078</v>
+        <v>0.8794262564694668</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7330587236270634</v>
+        <v>0.8835224107028979</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7699570044774416</v>
+        <v>0.8833406614799053</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7142460847558888</v>
+        <v>0.8878563660895891</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7666996153562151</v>
+        <v>0.8849252193409367</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7712245500741766</v>
+        <v>0.8896971853204358</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7738574804153884</v>
+        <v>0.8933739569977647</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7841888245205378</v>
+        <v>0.8933739569977647</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7911043572823876</v>
+        <v>0.8933739569977647</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7989006101940672</v>
+        <v>0.8728977169746726</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7945621236633125</v>
+        <v>0.8728977169746726</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7871572273426015</v>
+        <v>0.8769519161704784</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.78647688445247</v>
+        <v>0.8775950029871986</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.78647688445247</v>
+        <v>0.8801114661439629</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7859224066752144</v>
+        <v>0.8777208681000745</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7691462653303707</v>
+        <v>0.8789092025857729</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7630555686082339</v>
+        <v>0.8624967275070652</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7520858366505783</v>
+        <v>0.8709033423061174</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7597003403392653</v>
+        <v>0.872347938161631</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7463539394102128</v>
+        <v>0.8802514281494808</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7341911740026448</v>
+        <v>0.8760570991280066</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7502916714215709</v>
+        <v>0.8724642375259282</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.7565547194382723</v>
+        <v>0.8660566963596452</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7631487087917621</v>
+        <v>0.8660566963596452</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7784290691351892</v>
+        <v>0.8590527223784814</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.7800554142136955</v>
+        <v>0.8675341849646571</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6383104874168452</v>
+        <v>0.8618209157609973</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6251736938557686</v>
+        <v>0.8580182789707926</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.6344564976605871</v>
+        <v>0.868051238848351</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5498252992233283</v>
+        <v>0.858689223932496</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5455660238036102</v>
+        <v>0.8534468580711423</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5521180581194746</v>
+        <v>0.8352771381965376</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5491635843699024</v>
+        <v>0.8353377212708684</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5306585598345965</v>
+        <v>0.850529808215132</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5047439400143654</v>
+        <v>0.8500078875470736</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5028146795642047</v>
+        <v>0.8484421255428982</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5040402701233142</v>
+        <v>0.8497190690680612</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5039796870489833</v>
+        <v>0.8632331223274641</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5053264437567547</v>
+        <v>0.7742213145016749</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5057691533137767</v>
+        <v>0.7202063852210863</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5070553269472172</v>
+        <v>0.7202063852210863</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5069947438728863</v>
+        <v>0.723179487007364</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5034810933818445</v>
+        <v>0.6400346716430936</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5034810933818445</v>
+        <v>0.6101217367371735</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5039610590122777</v>
+        <v>0.5700172519114716</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5031362229725648</v>
+        <v>0.561396162960079</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5018500493391242</v>
+        <v>0.5522111983030027</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5022321758218153</v>
+        <v>0.5525327417113628</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5022321758218153</v>
+        <v>0.5534973719364431</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5024931361558446</v>
+        <v>0.5522111983030027</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4942635716155711</v>
+        <v>0.5502819378528419</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4950650806543643</v>
+        <v>0.5428864394605589</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4984948210701555</v>
+        <v>0.5428864394605589</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4985367761077809</v>
+        <v>0.5392888788942666</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4997390396659708</v>
+        <v>0.5421827695695077</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4997390396659708</v>
+        <v>0.5433291490175809</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4997390396659708</v>
+        <v>0.545305063469581</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4997390396659708</v>
+        <v>0.5316790741697937</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4997390396659708</v>
+        <v>0.5288179084239002</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4992171189979123</v>
+        <v>0.5287573253495694</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4992171189979123</v>
+        <v>0.5164733937933396</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5</v>
+        <v>0.5129642744463614</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5</v>
+        <v>0.5116222167028039</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5003215434083601</v>
+        <v>0.5109185468117527</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5003215434083601</v>
+        <v>0.5109185468117527</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5003215434083601</v>
+        <v>0.5016496720794259</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4992777020722432</v>
+        <v>0.5016496720794259</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5</v>
+        <v>0.5003634984459854</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5</v>
+        <v>0.499841577777927</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5</v>
+        <v>0.499841577777927</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5</v>
+        <v>0.5012861736334405</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5</v>
+        <v>0.5009646302250804</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5</v>
+        <v>0.5012861736334405</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5</v>
+        <v>0.5003215434083601</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5</v>
+        <v>0.5003215434083601</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5</v>
+        <v>0.5003215434083601</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5</v>
+        <v>0.5006430868167202</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5</v>
+        <v>0.5006430868167202</v>
       </c>
     </row>
     <row r="151">
@@ -1930,13 +1930,13 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5</v>
+        <v>0.5006430868167202</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -1946,7 +1946,7 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -1956,7 +1956,7 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -1966,7 +1966,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1976,7 +1976,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B156" t="n">
